--- a/PCB/PickAndPlace_PCB.xlsx
+++ b/PCB/PickAndPlace_PCB.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_PCB" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_PCB1_2026-05-07" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="162">
   <si>
     <t>Designator</t>
   </si>
@@ -94,16 +94,16 @@
     <t>SOT-223_L6.5-W3.5-P2.30-LS7.0-BR</t>
   </si>
   <si>
-    <t>47.886mm</t>
-  </si>
-  <si>
-    <t>-55.933mm</t>
-  </si>
-  <si>
-    <t>45.028mm</t>
-  </si>
-  <si>
-    <t>-53.633mm</t>
+    <t>45.339mm</t>
+  </si>
+  <si>
+    <t>-56.007mm</t>
+  </si>
+  <si>
+    <t>42.482mm</t>
+  </si>
+  <si>
+    <t>-53.707mm</t>
   </si>
   <si>
     <t>H1</t>
@@ -187,13 +187,13 @@
     <t>USB-C-SMD_TYPE-C16PIN</t>
   </si>
   <si>
-    <t>12.453mm</t>
+    <t>12.58mm</t>
   </si>
   <si>
     <t>-48.059mm</t>
   </si>
   <si>
-    <t>14.24mm</t>
+    <t>14.367mm</t>
   </si>
   <si>
     <t>-43.739mm</t>
@@ -208,13 +208,13 @@
     <t>C0603</t>
   </si>
   <si>
-    <t>38.361mm</t>
-  </si>
-  <si>
-    <t>-61.648mm</t>
-  </si>
-  <si>
-    <t>39.061mm</t>
+    <t>17.018mm</t>
+  </si>
+  <si>
+    <t>-51.308mm</t>
+  </si>
+  <si>
+    <t>16.318mm</t>
   </si>
   <si>
     <t>10uF</t>
@@ -226,13 +226,13 @@
     <t>CC0603KRX7R9BB104</t>
   </si>
   <si>
-    <t>18.422mm</t>
-  </si>
-  <si>
-    <t>-51.234mm</t>
-  </si>
-  <si>
-    <t>19.122mm</t>
+    <t>57.277mm</t>
+  </si>
+  <si>
+    <t>-66.802mm</t>
+  </si>
+  <si>
+    <t>56.577mm</t>
   </si>
   <si>
     <t>100nF</t>
@@ -241,25 +241,22 @@
     <t>C5</t>
   </si>
   <si>
-    <t>22.486mm</t>
-  </si>
-  <si>
-    <t>-53.139mm</t>
-  </si>
-  <si>
-    <t>21.786mm</t>
+    <t>52.197mm</t>
+  </si>
+  <si>
+    <t>-46.355mm</t>
+  </si>
+  <si>
+    <t>-47.055mm</t>
   </si>
   <si>
     <t>C6</t>
   </si>
   <si>
-    <t>41.536mm</t>
-  </si>
-  <si>
-    <t>-57.584mm</t>
-  </si>
-  <si>
-    <t>-58.284mm</t>
+    <t>51.689mm</t>
+  </si>
+  <si>
+    <t>-52.008mm</t>
   </si>
   <si>
     <t>LED1</t>
@@ -304,28 +301,25 @@
     <t>LED-SMD_4P-L5.0-W5.0-TL_WS2812B-B</t>
   </si>
   <si>
-    <t>34.551mm</t>
-  </si>
-  <si>
-    <t>-55.679mm</t>
-  </si>
-  <si>
-    <t>32.101mm</t>
-  </si>
-  <si>
-    <t>-54.029mm</t>
+    <t>31.877mm</t>
+  </si>
+  <si>
+    <t>29.427mm</t>
+  </si>
+  <si>
+    <t>-54.357mm</t>
   </si>
   <si>
     <t>C7</t>
   </si>
   <si>
-    <t>26.677mm</t>
-  </si>
-  <si>
-    <t>-60.886mm</t>
-  </si>
-  <si>
-    <t>-60.186mm</t>
+    <t>51.816mm</t>
+  </si>
+  <si>
+    <t>-55.88mm</t>
+  </si>
+  <si>
+    <t>-55.18mm</t>
   </si>
   <si>
     <t>R3</t>
@@ -337,13 +331,13 @@
     <t>R0603</t>
   </si>
   <si>
-    <t>45.466mm</t>
-  </si>
-  <si>
-    <t>-63.373mm</t>
-  </si>
-  <si>
-    <t>46.219mm</t>
+    <t>43.815mm</t>
+  </si>
+  <si>
+    <t>-63.119mm</t>
+  </si>
+  <si>
+    <t>44.568mm</t>
   </si>
   <si>
     <t>1kΩ</t>
@@ -355,13 +349,10 @@
     <t>FRC0603J331 TS</t>
   </si>
   <si>
-    <t>50.038mm</t>
-  </si>
-  <si>
-    <t>-63.246mm</t>
-  </si>
-  <si>
-    <t>50.791mm</t>
+    <t>49.276mm</t>
+  </si>
+  <si>
+    <t>50.029mm</t>
   </si>
   <si>
     <t>330Ω</t>
@@ -388,10 +379,13 @@
     <t>R8</t>
   </si>
   <si>
-    <t>-61.394mm</t>
-  </si>
-  <si>
-    <t>-62.147mm</t>
+    <t>26.162mm</t>
+  </si>
+  <si>
+    <t>-61.468mm</t>
+  </si>
+  <si>
+    <t>-62.221mm</t>
   </si>
   <si>
     <t>R9</t>
@@ -409,13 +403,13 @@
     <t>C1</t>
   </si>
   <si>
-    <t>72.009mm</t>
-  </si>
-  <si>
-    <t>-44.704mm</t>
-  </si>
-  <si>
-    <t>72.709mm</t>
+    <t>17.145mm</t>
+  </si>
+  <si>
+    <t>-45.72mm</t>
+  </si>
+  <si>
+    <t>17.845mm</t>
   </si>
   <si>
     <t>SDCARDSLOT</t>
@@ -442,13 +436,10 @@
     <t>R10</t>
   </si>
   <si>
-    <t>42.164mm</t>
-  </si>
-  <si>
-    <t>-62.357mm</t>
-  </si>
-  <si>
-    <t>41.411mm</t>
+    <t>-61.214mm</t>
+  </si>
+  <si>
+    <t>51.063mm</t>
   </si>
   <si>
     <t>C3</t>
@@ -460,13 +451,10 @@
     <t>C0805</t>
   </si>
   <si>
-    <t>28.122mm</t>
-  </si>
-  <si>
-    <t>-55.967mm</t>
-  </si>
-  <si>
-    <t>27.122mm</t>
+    <t>38.862mm</t>
+  </si>
+  <si>
+    <t>37.862mm</t>
   </si>
   <si>
     <t>22uF</t>
@@ -478,13 +466,10 @@
     <t>FRC0603F5101TS</t>
   </si>
   <si>
-    <t>17.78mm</t>
-  </si>
-  <si>
-    <t>-43.942mm</t>
-  </si>
-  <si>
-    <t>17.027mm</t>
+    <t>20.32mm</t>
+  </si>
+  <si>
+    <t>-47.108mm</t>
   </si>
   <si>
     <t>5.1kΩ</t>
@@ -493,25 +478,25 @@
     <t>R2</t>
   </si>
   <si>
-    <t>18.542mm</t>
-  </si>
-  <si>
-    <t>-46.355mm</t>
-  </si>
-  <si>
-    <t>17.789mm</t>
+    <t>17.907mm</t>
+  </si>
+  <si>
+    <t>-47.117mm</t>
+  </si>
+  <si>
+    <t>18.66mm</t>
   </si>
   <si>
     <t>R5</t>
   </si>
   <si>
-    <t>32.131mm</t>
-  </si>
-  <si>
-    <t>-61.214mm</t>
-  </si>
-  <si>
-    <t>31.378mm</t>
+    <t>34.036mm</t>
+  </si>
+  <si>
+    <t>-59.817mm</t>
+  </si>
+  <si>
+    <t>33.283mm</t>
   </si>
 </sst>
 </file>
@@ -1281,7 +1266,7 @@
         <v>21</v>
       </c>
       <c r="L9">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M9" t="s">
         <v>22</v>
@@ -1325,7 +1310,7 @@
         <v>21</v>
       </c>
       <c r="L10">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M10" t="s">
         <v>22</v>
@@ -1357,10 +1342,10 @@
         <v>77</v>
       </c>
       <c r="H11" t="s">
+        <v>76</v>
+      </c>
+      <c r="I11" t="s">
         <v>78</v>
-      </c>
-      <c r="I11" t="s">
-        <v>77</v>
       </c>
       <c r="J11">
         <v>2</v>
@@ -1369,7 +1354,7 @@
         <v>21</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M11" t="s">
         <v>22</v>
@@ -1392,19 +1377,19 @@
         <v>80</v>
       </c>
       <c r="E12" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="F12" t="s">
         <v>80</v>
       </c>
       <c r="G12" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="H12" t="s">
         <v>80</v>
       </c>
       <c r="I12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J12">
         <v>2</v>
@@ -1424,31 +1409,31 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" t="s">
         <v>83</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>84</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>85</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>86</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" t="s">
         <v>87</v>
       </c>
-      <c r="F13" t="s">
+      <c r="I13" t="s">
         <v>86</v>
-      </c>
-      <c r="G13" t="s">
-        <v>87</v>
-      </c>
-      <c r="H13" t="s">
-        <v>88</v>
-      </c>
-      <c r="I13" t="s">
-        <v>87</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -1463,36 +1448,36 @@
         <v>22</v>
       </c>
       <c r="N13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" t="s">
         <v>89</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>90</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>91</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
+        <v>86</v>
+      </c>
+      <c r="F14" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" t="s">
         <v>92</v>
       </c>
-      <c r="E14" t="s">
-        <v>87</v>
-      </c>
-      <c r="F14" t="s">
-        <v>92</v>
-      </c>
-      <c r="G14" t="s">
-        <v>87</v>
-      </c>
-      <c r="H14" t="s">
-        <v>93</v>
-      </c>
       <c r="I14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J14">
         <v>2</v>
@@ -1507,36 +1492,36 @@
         <v>22</v>
       </c>
       <c r="N14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" t="s">
         <v>94</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>95</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>96</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" t="s">
+        <v>96</v>
+      </c>
+      <c r="G15" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" t="s">
         <v>97</v>
       </c>
-      <c r="E15" t="s">
+      <c r="I15" t="s">
         <v>98</v>
-      </c>
-      <c r="F15" t="s">
-        <v>97</v>
-      </c>
-      <c r="G15" t="s">
-        <v>98</v>
-      </c>
-      <c r="H15" t="s">
-        <v>99</v>
-      </c>
-      <c r="I15" t="s">
-        <v>100</v>
       </c>
       <c r="J15">
         <v>4</v>
@@ -1551,12 +1536,12 @@
         <v>22</v>
       </c>
       <c r="N15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B16" t="s">
         <v>63</v>
@@ -1565,22 +1550,22 @@
         <v>64</v>
       </c>
       <c r="D16" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" t="s">
+        <v>100</v>
+      </c>
+      <c r="G16" t="s">
+        <v>101</v>
+      </c>
+      <c r="H16" t="s">
+        <v>100</v>
+      </c>
+      <c r="I16" t="s">
         <v>102</v>
-      </c>
-      <c r="E16" t="s">
-        <v>103</v>
-      </c>
-      <c r="F16" t="s">
-        <v>102</v>
-      </c>
-      <c r="G16" t="s">
-        <v>103</v>
-      </c>
-      <c r="H16" t="s">
-        <v>102</v>
-      </c>
-      <c r="I16" t="s">
-        <v>104</v>
       </c>
       <c r="J16">
         <v>2</v>
@@ -1600,31 +1585,31 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" t="s">
         <v>105</v>
       </c>
-      <c r="B17" t="s">
+      <c r="D17" t="s">
         <v>106</v>
       </c>
-      <c r="C17" t="s">
+      <c r="E17" t="s">
         <v>107</v>
       </c>
-      <c r="D17" t="s">
+      <c r="F17" t="s">
+        <v>106</v>
+      </c>
+      <c r="G17" t="s">
+        <v>107</v>
+      </c>
+      <c r="H17" t="s">
         <v>108</v>
       </c>
-      <c r="E17" t="s">
-        <v>109</v>
-      </c>
-      <c r="F17" t="s">
-        <v>108</v>
-      </c>
-      <c r="G17" t="s">
-        <v>109</v>
-      </c>
-      <c r="H17" t="s">
-        <v>110</v>
-      </c>
       <c r="I17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J17">
         <v>2</v>
@@ -1639,36 +1624,36 @@
         <v>22</v>
       </c>
       <c r="N17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>110</v>
+      </c>
+      <c r="B18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" t="s">
         <v>112</v>
       </c>
-      <c r="B18" t="s">
+      <c r="E18" t="s">
+        <v>107</v>
+      </c>
+      <c r="F18" t="s">
+        <v>112</v>
+      </c>
+      <c r="G18" t="s">
+        <v>107</v>
+      </c>
+      <c r="H18" t="s">
         <v>113</v>
       </c>
-      <c r="C18" t="s">
+      <c r="I18" t="s">
         <v>107</v>
-      </c>
-      <c r="D18" t="s">
-        <v>114</v>
-      </c>
-      <c r="E18" t="s">
-        <v>115</v>
-      </c>
-      <c r="F18" t="s">
-        <v>114</v>
-      </c>
-      <c r="G18" t="s">
-        <v>115</v>
-      </c>
-      <c r="H18" t="s">
-        <v>116</v>
-      </c>
-      <c r="I18" t="s">
-        <v>115</v>
       </c>
       <c r="J18">
         <v>2</v>
@@ -1683,36 +1668,36 @@
         <v>22</v>
       </c>
       <c r="N18" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C19" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" t="s">
+        <v>117</v>
+      </c>
+      <c r="E19" t="s">
         <v>118</v>
       </c>
-      <c r="B19" t="s">
+      <c r="F19" t="s">
+        <v>117</v>
+      </c>
+      <c r="G19" t="s">
+        <v>118</v>
+      </c>
+      <c r="H19" t="s">
+        <v>117</v>
+      </c>
+      <c r="I19" t="s">
         <v>119</v>
-      </c>
-      <c r="C19" t="s">
-        <v>107</v>
-      </c>
-      <c r="D19" t="s">
-        <v>120</v>
-      </c>
-      <c r="E19" t="s">
-        <v>121</v>
-      </c>
-      <c r="F19" t="s">
-        <v>120</v>
-      </c>
-      <c r="G19" t="s">
-        <v>121</v>
-      </c>
-      <c r="H19" t="s">
-        <v>120</v>
-      </c>
-      <c r="I19" t="s">
-        <v>122</v>
       </c>
       <c r="J19">
         <v>2</v>
@@ -1727,36 +1712,36 @@
         <v>22</v>
       </c>
       <c r="N19" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>121</v>
+      </c>
+      <c r="B20" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" t="s">
+        <v>122</v>
+      </c>
+      <c r="E20" t="s">
+        <v>123</v>
+      </c>
+      <c r="F20" t="s">
+        <v>122</v>
+      </c>
+      <c r="G20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H20" t="s">
+        <v>122</v>
+      </c>
+      <c r="I20" t="s">
         <v>124</v>
-      </c>
-      <c r="B20" t="s">
-        <v>119</v>
-      </c>
-      <c r="C20" t="s">
-        <v>107</v>
-      </c>
-      <c r="D20" t="s">
-        <v>120</v>
-      </c>
-      <c r="E20" t="s">
-        <v>125</v>
-      </c>
-      <c r="F20" t="s">
-        <v>120</v>
-      </c>
-      <c r="G20" t="s">
-        <v>125</v>
-      </c>
-      <c r="H20" t="s">
-        <v>120</v>
-      </c>
-      <c r="I20" t="s">
-        <v>126</v>
       </c>
       <c r="J20">
         <v>2</v>
@@ -1771,36 +1756,36 @@
         <v>22</v>
       </c>
       <c r="N20" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>125</v>
+      </c>
+      <c r="B21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C21" t="s">
+        <v>105</v>
+      </c>
+      <c r="D21" t="s">
+        <v>126</v>
+      </c>
+      <c r="E21" t="s">
         <v>127</v>
       </c>
-      <c r="B21" t="s">
-        <v>119</v>
-      </c>
-      <c r="C21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="F21" t="s">
+        <v>126</v>
+      </c>
+      <c r="G21" t="s">
+        <v>127</v>
+      </c>
+      <c r="H21" t="s">
+        <v>126</v>
+      </c>
+      <c r="I21" t="s">
         <v>128</v>
-      </c>
-      <c r="E21" t="s">
-        <v>129</v>
-      </c>
-      <c r="F21" t="s">
-        <v>128</v>
-      </c>
-      <c r="G21" t="s">
-        <v>129</v>
-      </c>
-      <c r="H21" t="s">
-        <v>128</v>
-      </c>
-      <c r="I21" t="s">
-        <v>130</v>
       </c>
       <c r="J21">
         <v>2</v>
@@ -1815,12 +1800,12 @@
         <v>22</v>
       </c>
       <c r="N21" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B22" t="s">
         <v>63</v>
@@ -1829,22 +1814,22 @@
         <v>64</v>
       </c>
       <c r="D22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E22" t="s">
+        <v>131</v>
+      </c>
+      <c r="F22" t="s">
+        <v>130</v>
+      </c>
+      <c r="G22" t="s">
+        <v>131</v>
+      </c>
+      <c r="H22" t="s">
         <v>132</v>
       </c>
-      <c r="E22" t="s">
-        <v>133</v>
-      </c>
-      <c r="F22" t="s">
-        <v>132</v>
-      </c>
-      <c r="G22" t="s">
-        <v>133</v>
-      </c>
-      <c r="H22" t="s">
-        <v>134</v>
-      </c>
       <c r="I22" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J22">
         <v>2</v>
@@ -1864,31 +1849,31 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>133</v>
+      </c>
+      <c r="B23" t="s">
+        <v>134</v>
+      </c>
+      <c r="C23" t="s">
         <v>135</v>
       </c>
-      <c r="B23" t="s">
+      <c r="D23" t="s">
         <v>136</v>
       </c>
-      <c r="C23" t="s">
+      <c r="E23" t="s">
         <v>137</v>
       </c>
-      <c r="D23" t="s">
+      <c r="F23" t="s">
+        <v>136</v>
+      </c>
+      <c r="G23" t="s">
+        <v>137</v>
+      </c>
+      <c r="H23" t="s">
         <v>138</v>
       </c>
-      <c r="E23" t="s">
+      <c r="I23" t="s">
         <v>139</v>
-      </c>
-      <c r="F23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G23" t="s">
-        <v>139</v>
-      </c>
-      <c r="H23" t="s">
-        <v>140</v>
-      </c>
-      <c r="I23" t="s">
-        <v>141</v>
       </c>
       <c r="J23">
         <v>13</v>
@@ -1903,36 +1888,36 @@
         <v>22</v>
       </c>
       <c r="N23" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>140</v>
+      </c>
+      <c r="B24" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24" t="s">
+        <v>105</v>
+      </c>
+      <c r="D24" t="s">
+        <v>100</v>
+      </c>
+      <c r="E24" t="s">
+        <v>141</v>
+      </c>
+      <c r="F24" t="s">
+        <v>100</v>
+      </c>
+      <c r="G24" t="s">
+        <v>141</v>
+      </c>
+      <c r="H24" t="s">
         <v>142</v>
       </c>
-      <c r="B24" t="s">
-        <v>113</v>
-      </c>
-      <c r="C24" t="s">
-        <v>107</v>
-      </c>
-      <c r="D24" t="s">
-        <v>143</v>
-      </c>
-      <c r="E24" t="s">
-        <v>144</v>
-      </c>
-      <c r="F24" t="s">
-        <v>143</v>
-      </c>
-      <c r="G24" t="s">
-        <v>144</v>
-      </c>
-      <c r="H24" t="s">
-        <v>145</v>
-      </c>
       <c r="I24" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J24">
         <v>2</v>
@@ -1947,36 +1932,36 @@
         <v>22</v>
       </c>
       <c r="N24" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>143</v>
+      </c>
+      <c r="B25" t="s">
+        <v>144</v>
+      </c>
+      <c r="C25" t="s">
+        <v>145</v>
+      </c>
+      <c r="D25" t="s">
         <v>146</v>
       </c>
-      <c r="B25" t="s">
+      <c r="E25" t="s">
+        <v>28</v>
+      </c>
+      <c r="F25" t="s">
+        <v>146</v>
+      </c>
+      <c r="G25" t="s">
+        <v>28</v>
+      </c>
+      <c r="H25" t="s">
         <v>147</v>
       </c>
-      <c r="C25" t="s">
-        <v>148</v>
-      </c>
-      <c r="D25" t="s">
-        <v>149</v>
-      </c>
-      <c r="E25" t="s">
-        <v>150</v>
-      </c>
-      <c r="F25" t="s">
-        <v>149</v>
-      </c>
-      <c r="G25" t="s">
-        <v>150</v>
-      </c>
-      <c r="H25" t="s">
-        <v>151</v>
-      </c>
       <c r="I25" t="s">
-        <v>150</v>
+        <v>28</v>
       </c>
       <c r="J25">
         <v>2</v>
@@ -1991,36 +1976,36 @@
         <v>22</v>
       </c>
       <c r="N25" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B26" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D26" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E26" t="s">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="F26" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G26" t="s">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="H26" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="I26" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="J26">
         <v>2</v>
@@ -2029,42 +2014,42 @@
         <v>21</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M26" t="s">
         <v>22</v>
       </c>
       <c r="N26" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B27" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D27" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E27" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F27" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G27" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="H27" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I27" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="J27">
         <v>2</v>
@@ -2073,42 +2058,42 @@
         <v>21</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M27" t="s">
         <v>22</v>
       </c>
       <c r="N27" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B28" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D28" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E28" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F28" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G28" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H28" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="I28" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="J28">
         <v>2</v>
@@ -2123,7 +2108,7 @@
         <v>22</v>
       </c>
       <c r="N28" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
